--- a/artfynd/A 27380-2024 artfynd.xlsx
+++ b/artfynd/A 27380-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749551</v>
+        <v>119749711</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>91836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,27 +1055,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588619</v>
+        <v>588713</v>
       </c>
       <c r="R5" t="n">
-        <v>6435746</v>
+        <v>6435633</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749678</v>
+        <v>119749551</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,48 +1258,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588681</v>
+        <v>588619</v>
       </c>
       <c r="R7" t="n">
-        <v>6435638</v>
+        <v>6435746</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1338,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749711</v>
+        <v>119749678</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>90582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,35 +1368,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588713</v>
+        <v>588681</v>
       </c>
       <c r="R8" t="n">
-        <v>6435633</v>
+        <v>6435638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 27380-2024 artfynd.xlsx
+++ b/artfynd/A 27380-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749744</v>
+        <v>119749551</v>
       </c>
       <c r="B2" t="n">
         <v>57463</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588713</v>
+        <v>588619</v>
       </c>
       <c r="R2" t="n">
-        <v>6435633</v>
+        <v>6435746</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119750334</v>
+        <v>119749942</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -824,12 +824,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588653</v>
+        <v>588729</v>
       </c>
       <c r="R3" t="n">
-        <v>6435669</v>
+        <v>6435582</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749942</v>
+        <v>119749678</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588729</v>
+        <v>588681</v>
       </c>
       <c r="R4" t="n">
-        <v>6435582</v>
+        <v>6435638</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749711</v>
+        <v>119749775</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,38 +1029,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588713</v>
+        <v>588716</v>
       </c>
       <c r="R5" t="n">
-        <v>6435633</v>
+        <v>6435602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749775</v>
+        <v>119749744</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1140,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588716</v>
+        <v>588713</v>
       </c>
       <c r="R6" t="n">
-        <v>6435602</v>
+        <v>6435633</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1224,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749551</v>
+        <v>119750334</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,24 +1280,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588619</v>
+        <v>588653</v>
       </c>
       <c r="R7" t="n">
-        <v>6435746</v>
+        <v>6435669</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,6 +1337,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749678</v>
+        <v>119749711</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>91836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,35 +1368,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588681</v>
+        <v>588713</v>
       </c>
       <c r="R8" t="n">
-        <v>6435638</v>
+        <v>6435633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 27380-2024 artfynd.xlsx
+++ b/artfynd/A 27380-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749551</v>
+        <v>119749711</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>91836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +713,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588619</v>
+        <v>588713</v>
       </c>
       <c r="R2" t="n">
-        <v>6435746</v>
+        <v>6435633</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749942</v>
+        <v>119749744</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588729</v>
+        <v>588713</v>
       </c>
       <c r="R3" t="n">
-        <v>6435582</v>
+        <v>6435633</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749678</v>
+        <v>119749551</v>
       </c>
       <c r="B4" t="n">
-        <v>90582</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,48 +919,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588681</v>
+        <v>588619</v>
       </c>
       <c r="R4" t="n">
-        <v>6435638</v>
+        <v>6435746</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749775</v>
+        <v>119749678</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,35 +1029,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588716</v>
+        <v>588681</v>
       </c>
       <c r="R5" t="n">
-        <v>6435602</v>
+        <v>6435638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119749744</v>
+        <v>119750334</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,39 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588713</v>
+        <v>588653</v>
       </c>
       <c r="R6" t="n">
-        <v>6435633</v>
+        <v>6435669</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1224,6 +1226,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119750334</v>
+        <v>119749775</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1257,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588653</v>
+        <v>588716</v>
       </c>
       <c r="R7" t="n">
-        <v>6435669</v>
+        <v>6435602</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749711</v>
+        <v>119749942</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,31 +1372,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588713</v>
+        <v>588729</v>
       </c>
       <c r="R8" t="n">
-        <v>6435633</v>
+        <v>6435582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 27380-2024 artfynd.xlsx
+++ b/artfynd/A 27380-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119749711</v>
+        <v>119749678</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588713</v>
+        <v>588681</v>
       </c>
       <c r="R2" t="n">
-        <v>6435633</v>
+        <v>6435638</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119749744</v>
+        <v>119750334</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588713</v>
+        <v>588653</v>
       </c>
       <c r="R3" t="n">
-        <v>6435633</v>
+        <v>6435669</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119749551</v>
+        <v>119749775</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,53 +915,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588619</v>
+        <v>588716</v>
       </c>
       <c r="R4" t="n">
-        <v>6435746</v>
+        <v>6435602</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119749678</v>
+        <v>119749711</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>91854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,35 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588681</v>
+        <v>588713</v>
       </c>
       <c r="R5" t="n">
-        <v>6435638</v>
+        <v>6435633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119750334</v>
+        <v>119749744</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,38 +1140,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588653</v>
+        <v>588713</v>
       </c>
       <c r="R6" t="n">
-        <v>6435669</v>
+        <v>6435633</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,7 +1224,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119749775</v>
+        <v>119749942</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,35 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588716</v>
+        <v>588729</v>
       </c>
       <c r="R7" t="n">
-        <v>6435602</v>
+        <v>6435582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119749942</v>
+        <v>119749551</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,52 +1368,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588729</v>
+        <v>588619</v>
       </c>
       <c r="R8" t="n">
-        <v>6435582</v>
+        <v>6435746</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1452,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
